--- a/data_pur.xlsx
+++ b/data_pur.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ali\belajar python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4F0DA1-3606-46EF-B0C5-CD96B2CAF82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62376AC-1F40-4F28-B2C0-2176A1243298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5539,7 +5539,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T721"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
@@ -5562,7 +5562,7 @@
     <col min="20" max="20" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5659,7 +5659,7 @@
         <v>45798</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>45798</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5782,7 +5782,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5870,7 +5870,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5914,7 +5914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5958,7 +5958,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6037,7 +6037,7 @@
         <v>45838</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>45838</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>45838</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>45838</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6177,7 +6177,7 @@
         <v>45838</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6230,7 +6230,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6389,7 +6389,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6707,7 +6707,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6760,7 +6760,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -6866,7 +6866,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6972,7 +6972,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -7078,7 +7078,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -7131,7 +7131,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -7184,7 +7184,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -7237,7 +7237,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -7343,7 +7343,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -7396,7 +7396,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -7449,7 +7449,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -7502,7 +7502,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -7661,7 +7661,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -7714,7 +7714,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -7767,7 +7767,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7820,7 +7820,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -7873,7 +7873,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7926,7 +7926,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -7979,7 +7979,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -8032,7 +8032,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -8085,7 +8085,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -8138,7 +8138,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -8191,7 +8191,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -8244,7 +8244,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -8297,7 +8297,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -8350,7 +8350,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -8403,7 +8403,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -8456,7 +8456,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -8509,7 +8509,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -8615,7 +8615,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -8668,7 +8668,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -8827,7 +8827,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -8880,7 +8880,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -8933,7 +8933,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -8986,7 +8986,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -9039,7 +9039,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9092,7 +9092,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -9251,7 +9251,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -9357,7 +9357,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -9410,7 +9410,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -9463,7 +9463,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -9516,7 +9516,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="79" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -9569,7 +9569,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="80" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -9622,7 +9622,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -9728,7 +9728,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -9781,7 +9781,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -9887,7 +9887,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -9940,7 +9940,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -9993,7 +9993,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -10046,7 +10046,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -10099,7 +10099,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -10152,7 +10152,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -10205,7 +10205,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -10258,7 +10258,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -10311,7 +10311,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -10364,7 +10364,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -10417,7 +10417,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -10470,7 +10470,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -10523,7 +10523,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -10576,7 +10576,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -10629,7 +10629,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -10682,7 +10682,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -10735,7 +10735,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -10788,7 +10788,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -10841,7 +10841,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="104" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="105" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -11000,7 +11000,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -11053,7 +11053,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -11106,7 +11106,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="109" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -11159,7 +11159,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -11265,7 +11265,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -11318,7 +11318,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="113" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -11371,7 +11371,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="115" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -11477,7 +11477,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="116" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -11530,7 +11530,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="117" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -11583,7 +11583,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="118" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -11636,7 +11636,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="119" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -11689,7 +11689,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="120" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -11742,7 +11742,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="121" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -11795,7 +11795,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -11848,7 +11848,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="123" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -11895,7 +11895,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="124" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="125" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -11989,7 +11989,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="126" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -12036,7 +12036,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="127" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -12083,7 +12083,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="128" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -12130,7 +12130,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -12177,7 +12177,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -12224,7 +12224,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -12271,7 +12271,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -12318,7 +12318,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -12365,7 +12365,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -12412,7 +12412,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -12459,7 +12459,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -12506,7 +12506,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -12553,7 +12553,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -12600,7 +12600,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -12647,7 +12647,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -12694,7 +12694,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -12788,7 +12788,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -12835,7 +12835,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -12882,7 +12882,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="145" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -12929,7 +12929,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="146" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -12976,7 +12976,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="147" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -13023,7 +13023,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="148" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -13070,7 +13070,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="149" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -13117,7 +13117,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="150" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -13167,7 +13167,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="151" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -13226,7 +13226,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="152" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -13282,7 +13282,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="153" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -13338,7 +13338,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -13394,7 +13394,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="155" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -13450,7 +13450,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="156" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -13506,7 +13506,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="157" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -13562,7 +13562,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="158" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -13615,7 +13615,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="159" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -13671,7 +13671,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="160" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -13727,7 +13727,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="161" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -13783,7 +13783,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="162" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -13839,7 +13839,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="163" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -13895,7 +13895,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="164" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -13951,7 +13951,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="165" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -14007,7 +14007,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="166" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -14063,7 +14063,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="167" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -14119,7 +14119,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="168" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -14172,7 +14172,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="169" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -14228,7 +14228,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="170" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -14284,7 +14284,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="171" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="172" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -14396,7 +14396,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="173" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -14452,7 +14452,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="174" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -14508,7 +14508,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="175" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -14564,7 +14564,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="176" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -14623,7 +14623,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="177" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -14679,7 +14679,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="178" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -14735,7 +14735,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="179" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -14791,7 +14791,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="180" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -14847,7 +14847,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="181" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -14903,7 +14903,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="182" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -14959,7 +14959,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="183" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -15015,7 +15015,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="184" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -15071,7 +15071,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="185" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -15127,7 +15127,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="186" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -15183,7 +15183,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="187" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -15236,7 +15236,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="188" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -15292,7 +15292,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="189" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -15348,7 +15348,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="190" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -15401,7 +15401,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="191" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -15457,7 +15457,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="192" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -15513,7 +15513,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="193" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -15566,7 +15566,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="194" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -15622,7 +15622,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="195" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -15675,7 +15675,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="196" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -15731,7 +15731,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="197" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -15784,7 +15784,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="198" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -15840,7 +15840,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="199" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -15896,7 +15896,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="200" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -15952,7 +15952,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="201" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -16008,7 +16008,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="202" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -16064,7 +16064,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="203" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -16120,7 +16120,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="204" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -16176,7 +16176,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="205" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -16232,7 +16232,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="206" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -16288,7 +16288,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="207" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -16344,7 +16344,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="208" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -16397,7 +16397,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="209" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -16453,7 +16453,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="210" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -16509,7 +16509,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="211" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -16565,7 +16565,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="212" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -16621,7 +16621,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="213" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -16677,7 +16677,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="214" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -16733,7 +16733,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="215" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -16789,7 +16789,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="216" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -16845,7 +16845,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="217" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -16901,7 +16901,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="218" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -16957,7 +16957,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="219" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -17013,7 +17013,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="220" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -17069,7 +17069,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="221" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -17125,7 +17125,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="222" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -17181,7 +17181,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="223" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -17237,7 +17237,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="224" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -17293,7 +17293,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="225" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -17349,7 +17349,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="226" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -17405,7 +17405,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="227" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -17461,7 +17461,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="228" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -17517,7 +17517,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="229" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -17573,7 +17573,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="230" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -17629,7 +17629,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="231" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -17685,7 +17685,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="232" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -17741,7 +17741,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="233" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -17791,7 +17791,7 @@
         <v>46009</v>
       </c>
     </row>
-    <row r="234" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -17841,7 +17841,7 @@
         <v>46009</v>
       </c>
     </row>
-    <row r="235" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -17897,7 +17897,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="236" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -17953,7 +17953,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="237" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -18009,7 +18009,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="238" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -18068,7 +18068,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="239" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -18124,7 +18124,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="240" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -18177,7 +18177,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="241" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -18233,7 +18233,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="242" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -18289,7 +18289,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="243" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -18345,7 +18345,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="244" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -18401,7 +18401,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="245" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -18457,7 +18457,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="246" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -18513,7 +18513,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="247" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -18569,7 +18569,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="248" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
@@ -18625,7 +18625,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="249" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -18681,7 +18681,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="250" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -18737,7 +18737,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="251" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -18793,7 +18793,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="252" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -18849,7 +18849,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="253" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -18905,7 +18905,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="254" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -18955,7 +18955,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="255" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -19005,7 +19005,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="256" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -19055,7 +19055,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="257" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -19105,7 +19105,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="258" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -19155,7 +19155,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="259" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -19205,7 +19205,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="260" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -19255,7 +19255,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="261" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -19305,7 +19305,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="262" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -19355,7 +19355,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="263" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -19408,7 +19408,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="264" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -19464,7 +19464,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="265" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -19520,7 +19520,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="266" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -19576,7 +19576,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="267" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -19632,7 +19632,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="268" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -19688,7 +19688,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="269" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -19744,7 +19744,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="270" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -19800,7 +19800,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="271" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -19853,7 +19853,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="272" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -19909,7 +19909,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="273" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -19965,7 +19965,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="274" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -20021,7 +20021,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="275" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -20074,7 +20074,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="276" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -20130,7 +20130,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="277" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
@@ -20186,7 +20186,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="278" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
@@ -20242,7 +20242,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="279" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
@@ -20301,7 +20301,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="280" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
@@ -20354,7 +20354,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="281" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
@@ -20404,7 +20404,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="282" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -20457,7 +20457,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="283" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>282</v>
       </c>
@@ -20510,7 +20510,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="284" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
@@ -20563,7 +20563,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="285" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
@@ -20616,7 +20616,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="286" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>285</v>
       </c>
@@ -20669,7 +20669,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="287" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
@@ -20719,7 +20719,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="288" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>287</v>
       </c>
@@ -20769,7 +20769,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="289" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>
@@ -20822,7 +20822,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="290" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>289</v>
       </c>
@@ -20881,7 +20881,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="291" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>290</v>
       </c>
@@ -20940,7 +20940,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="292" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>291</v>
       </c>
@@ -20999,7 +20999,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="293" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>292</v>
       </c>
@@ -21058,7 +21058,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="294" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>293</v>
       </c>
@@ -21117,7 +21117,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="295" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>294</v>
       </c>
@@ -21176,7 +21176,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="296" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>295</v>
       </c>
@@ -21235,7 +21235,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="297" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>296</v>
       </c>
@@ -21294,7 +21294,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="298" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>297</v>
       </c>
@@ -21353,7 +21353,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="299" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>298</v>
       </c>
@@ -21412,7 +21412,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="300" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>299</v>
       </c>
@@ -21471,7 +21471,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="301" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>300</v>
       </c>
@@ -21527,7 +21527,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="302" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>301</v>
       </c>
@@ -21583,7 +21583,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="303" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>302</v>
       </c>
@@ -21639,7 +21639,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="304" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>303</v>
       </c>
@@ -21692,7 +21692,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="305" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>304</v>
       </c>
@@ -21748,7 +21748,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="306" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>305</v>
       </c>
@@ -21801,7 +21801,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="307" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>306</v>
       </c>
@@ -21857,7 +21857,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="308" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>307</v>
       </c>
@@ -21913,7 +21913,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="309" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>308</v>
       </c>
@@ -21969,7 +21969,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="310" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>309</v>
       </c>
@@ -22025,7 +22025,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="311" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>310</v>
       </c>
@@ -22081,7 +22081,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="312" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>311</v>
       </c>
@@ -22137,7 +22137,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="313" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>312</v>
       </c>
@@ -22187,7 +22187,7 @@
         <v>46011</v>
       </c>
     </row>
-    <row r="314" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>313</v>
       </c>
@@ -22243,7 +22243,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="315" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>314</v>
       </c>
@@ -22299,7 +22299,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="316" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>315</v>
       </c>
@@ -22355,7 +22355,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="317" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>316</v>
       </c>
@@ -22411,7 +22411,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="318" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>317</v>
       </c>
@@ -22467,7 +22467,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="319" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>318</v>
       </c>
@@ -22520,7 +22520,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="320" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>319</v>
       </c>
@@ -22576,7 +22576,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="321" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>320</v>
       </c>
@@ -22629,7 +22629,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="322" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>321</v>
       </c>
@@ -22685,7 +22685,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="323" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>322</v>
       </c>
@@ -22741,7 +22741,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="324" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>323</v>
       </c>
@@ -22797,7 +22797,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="325" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>324</v>
       </c>
@@ -22853,7 +22853,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="326" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>325</v>
       </c>
@@ -22906,7 +22906,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="327" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>326</v>
       </c>
@@ -22962,7 +22962,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="328" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>327</v>
       </c>
@@ -23015,7 +23015,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="329" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>328</v>
       </c>
@@ -23068,7 +23068,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="330" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>329</v>
       </c>
@@ -23124,7 +23124,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="331" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>330</v>
       </c>
@@ -23180,7 +23180,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="332" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>331</v>
       </c>
@@ -23236,7 +23236,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="333" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>332</v>
       </c>
@@ -23292,7 +23292,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="334" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>333</v>
       </c>
@@ -23348,7 +23348,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="335" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>334</v>
       </c>
@@ -23404,7 +23404,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="336" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>335</v>
       </c>
@@ -23460,7 +23460,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="337" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>336</v>
       </c>
@@ -23516,7 +23516,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="338" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>337</v>
       </c>
@@ -23572,7 +23572,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="339" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>338</v>
       </c>
@@ -23628,7 +23628,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="340" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>339</v>
       </c>
@@ -23684,7 +23684,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="341" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>340</v>
       </c>
@@ -23740,7 +23740,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="342" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>341</v>
       </c>
@@ -23796,7 +23796,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="343" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>342</v>
       </c>
@@ -23852,7 +23852,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="344" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>343</v>
       </c>
@@ -23908,7 +23908,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="345" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>344</v>
       </c>
@@ -23964,7 +23964,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="346" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>345</v>
       </c>
@@ -24023,7 +24023,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="347" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>346</v>
       </c>
@@ -24082,7 +24082,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="348" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>347</v>
       </c>
@@ -24141,7 +24141,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="349" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>348</v>
       </c>
@@ -24200,7 +24200,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="350" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>349</v>
       </c>
@@ -24247,7 +24247,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="351" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>350</v>
       </c>
@@ -24303,7 +24303,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="352" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>351</v>
       </c>
@@ -24359,7 +24359,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="353" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>352</v>
       </c>
@@ -24412,7 +24412,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="354" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>353</v>
       </c>
@@ -24471,7 +24471,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="355" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>354</v>
       </c>
@@ -24530,7 +24530,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="356" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>355</v>
       </c>
@@ -24589,7 +24589,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="357" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>356</v>
       </c>
@@ -24648,7 +24648,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="358" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>357</v>
       </c>
@@ -24704,7 +24704,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="359" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>358</v>
       </c>
@@ -24760,7 +24760,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="360" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>359</v>
       </c>
@@ -24816,7 +24816,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="361" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>360</v>
       </c>
@@ -24869,7 +24869,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="362" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>361</v>
       </c>
@@ -24925,7 +24925,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="363" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>362</v>
       </c>
@@ -24981,7 +24981,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="364" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>363</v>
       </c>
@@ -25034,7 +25034,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="365" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>364</v>
       </c>
@@ -25090,7 +25090,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="366" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>365</v>
       </c>
@@ -25146,7 +25146,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="367" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>366</v>
       </c>
@@ -25202,7 +25202,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="368" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>367</v>
       </c>
@@ -25255,7 +25255,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="369" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>368</v>
       </c>
@@ -25308,7 +25308,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="370" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>369</v>
       </c>
@@ -25364,7 +25364,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="371" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>370</v>
       </c>
@@ -25420,7 +25420,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="372" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>371</v>
       </c>
@@ -25476,7 +25476,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="373" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>372</v>
       </c>
@@ -25532,7 +25532,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="374" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>373</v>
       </c>
@@ -25588,7 +25588,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="375" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>374</v>
       </c>
@@ -25644,7 +25644,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="376" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>375</v>
       </c>
@@ -25697,7 +25697,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="377" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>376</v>
       </c>
@@ -25750,7 +25750,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="378" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>377</v>
       </c>
@@ -25806,7 +25806,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="379" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>378</v>
       </c>
@@ -25865,7 +25865,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="380" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>379</v>
       </c>
@@ -25918,7 +25918,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="381" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>380</v>
       </c>
@@ -25974,7 +25974,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="382" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>381</v>
       </c>
@@ -26030,7 +26030,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="383" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>382</v>
       </c>
@@ -26086,7 +26086,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="384" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>383</v>
       </c>
@@ -26142,7 +26142,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="385" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>384</v>
       </c>
@@ -26198,7 +26198,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="386" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>385</v>
       </c>
@@ -26254,7 +26254,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="387" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>386</v>
       </c>
@@ -26310,7 +26310,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="388" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>387</v>
       </c>
@@ -26366,7 +26366,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="389" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>388</v>
       </c>
@@ -26422,7 +26422,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="390" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>389</v>
       </c>
@@ -26478,7 +26478,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="391" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>390</v>
       </c>
@@ -26537,7 +26537,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="392" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>391</v>
       </c>
@@ -26596,7 +26596,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="393" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>392</v>
       </c>
@@ -26649,7 +26649,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="394" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>393</v>
       </c>
@@ -26705,7 +26705,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="395" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>394</v>
       </c>
@@ -26758,7 +26758,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="396" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>395</v>
       </c>
@@ -26811,7 +26811,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="397" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>396</v>
       </c>
@@ -26864,7 +26864,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="398" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>397</v>
       </c>
@@ -26917,7 +26917,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="399" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>398</v>
       </c>
@@ -26970,7 +26970,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="400" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>399</v>
       </c>
@@ -27026,7 +27026,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="401" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>400</v>
       </c>
@@ -27079,7 +27079,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="402" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>401</v>
       </c>
@@ -27135,7 +27135,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="403" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>402</v>
       </c>
@@ -27188,7 +27188,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="404" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>403</v>
       </c>
@@ -27244,7 +27244,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="405" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>404</v>
       </c>
@@ -27300,7 +27300,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="406" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>405</v>
       </c>
@@ -27356,7 +27356,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="407" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>406</v>
       </c>
@@ -27409,7 +27409,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="408" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>407</v>
       </c>
@@ -27465,7 +27465,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="409" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>408</v>
       </c>
@@ -27518,7 +27518,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="410" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>409</v>
       </c>
@@ -27571,7 +27571,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="411" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>410</v>
       </c>
@@ -27624,7 +27624,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="412" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>411</v>
       </c>
@@ -27674,7 +27674,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="413" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>412</v>
       </c>
@@ -27727,7 +27727,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="414" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>413</v>
       </c>
@@ -27774,7 +27774,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="415" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>414</v>
       </c>
@@ -27830,7 +27830,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="416" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>415</v>
       </c>
@@ -27886,7 +27886,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="417" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>416</v>
       </c>
@@ -27945,7 +27945,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="418" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>417</v>
       </c>
@@ -27998,7 +27998,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="419" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>418</v>
       </c>
@@ -28051,7 +28051,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="420" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>419</v>
       </c>
@@ -28107,7 +28107,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="421" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>420</v>
       </c>
@@ -28163,7 +28163,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="422" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>421</v>
       </c>
@@ -28216,7 +28216,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="423" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>422</v>
       </c>
@@ -28269,7 +28269,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="424" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>423</v>
       </c>
@@ -28325,7 +28325,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="425" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>424</v>
       </c>
@@ -28375,7 +28375,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="426" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>425</v>
       </c>
@@ -28431,7 +28431,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="427" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>426</v>
       </c>
@@ -28481,7 +28481,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="428" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>427</v>
       </c>
@@ -28537,7 +28537,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="429" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>428</v>
       </c>
@@ -28593,7 +28593,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="430" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>429</v>
       </c>
@@ -28649,7 +28649,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="431" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>430</v>
       </c>
@@ -28702,7 +28702,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="432" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>431</v>
       </c>
@@ -28755,7 +28755,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="433" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>432</v>
       </c>
@@ -28808,7 +28808,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="434" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>433</v>
       </c>
@@ -28855,7 +28855,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="435" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>434</v>
       </c>
@@ -28905,7 +28905,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="436" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>435</v>
       </c>
@@ -28952,7 +28952,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="437" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>436</v>
       </c>
@@ -29008,7 +29008,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="438" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>437</v>
       </c>
@@ -29064,7 +29064,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="439" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>438</v>
       </c>
@@ -29120,7 +29120,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="440" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>439</v>
       </c>
@@ -29176,7 +29176,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="441" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>440</v>
       </c>
@@ -29232,7 +29232,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="442" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>441</v>
       </c>
@@ -29288,7 +29288,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="443" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>442</v>
       </c>
@@ -29341,7 +29341,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="444" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>443</v>
       </c>
@@ -29397,7 +29397,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="445" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>444</v>
       </c>
@@ -29453,7 +29453,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="446" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>445</v>
       </c>
@@ -29509,7 +29509,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="447" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>446</v>
       </c>
@@ -29562,7 +29562,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="448" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>447</v>
       </c>
@@ -29615,7 +29615,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="449" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>448</v>
       </c>
@@ -29671,7 +29671,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="450" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>449</v>
       </c>
@@ -29727,7 +29727,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="451" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>450</v>
       </c>
@@ -29780,7 +29780,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="452" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>451</v>
       </c>
@@ -29833,7 +29833,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="453" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>452</v>
       </c>
@@ -29886,7 +29886,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="454" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>453</v>
       </c>
@@ -29942,7 +29942,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="455" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>454</v>
       </c>
@@ -29995,7 +29995,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="456" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>455</v>
       </c>
@@ -30051,7 +30051,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="457" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>456</v>
       </c>
@@ -30104,7 +30104,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="458" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>457</v>
       </c>
@@ -30157,7 +30157,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="459" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>458</v>
       </c>
@@ -30210,7 +30210,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="460" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>459</v>
       </c>
@@ -30266,7 +30266,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="461" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>460</v>
       </c>
@@ -30322,7 +30322,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="462" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>461</v>
       </c>
@@ -30375,7 +30375,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="463" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>462</v>
       </c>
@@ -30431,7 +30431,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="464" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>463</v>
       </c>
@@ -30484,7 +30484,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="465" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>464</v>
       </c>
@@ -30540,7 +30540,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="466" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>465</v>
       </c>
@@ -30596,7 +30596,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="467" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>466</v>
       </c>
@@ -30652,7 +30652,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="468" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>467</v>
       </c>
@@ -30708,7 +30708,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="469" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>468</v>
       </c>
@@ -30761,7 +30761,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="470" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>469</v>
       </c>
@@ -30817,7 +30817,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="471" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>470</v>
       </c>
@@ -30873,7 +30873,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="472" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>471</v>
       </c>
@@ -30929,7 +30929,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="473" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>472</v>
       </c>
@@ -30982,7 +30982,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="474" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>473</v>
       </c>
@@ -31035,7 +31035,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="475" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>474</v>
       </c>
@@ -31088,7 +31088,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="476" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>475</v>
       </c>
@@ -31141,7 +31141,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="477" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>476</v>
       </c>
@@ -31185,7 +31185,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="478" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>477</v>
       </c>
@@ -31241,7 +31241,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="479" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>478</v>
       </c>
@@ -31294,7 +31294,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="480" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>479</v>
       </c>
@@ -31350,7 +31350,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="481" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>480</v>
       </c>
@@ -31403,7 +31403,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="482" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>481</v>
       </c>
@@ -31462,7 +31462,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="483" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>482</v>
       </c>
@@ -31515,7 +31515,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="484" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>483</v>
       </c>
@@ -31562,7 +31562,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="485" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>484</v>
       </c>
@@ -31612,7 +31612,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="486" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>485</v>
       </c>
@@ -31662,7 +31662,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="487" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>486</v>
       </c>
@@ -31709,7 +31709,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="488" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>487</v>
       </c>
@@ -31756,7 +31756,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="489" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>488</v>
       </c>
@@ -31803,7 +31803,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="490" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>489</v>
       </c>
@@ -31850,7 +31850,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="491" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>490</v>
       </c>
@@ -31897,7 +31897,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="492" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>491</v>
       </c>
@@ -31944,7 +31944,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="493" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>492</v>
       </c>
@@ -31991,7 +31991,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="494" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>493</v>
       </c>
@@ -32038,7 +32038,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="495" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>494</v>
       </c>
@@ -32085,7 +32085,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="496" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>495</v>
       </c>
@@ -32132,7 +32132,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="497" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>496</v>
       </c>
@@ -32179,7 +32179,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="498" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>497</v>
       </c>
@@ -32226,7 +32226,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="499" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>498</v>
       </c>
@@ -32282,7 +32282,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="500" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>499</v>
       </c>
@@ -32329,7 +32329,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="501" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>500</v>
       </c>
@@ -32379,7 +32379,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="502" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>501</v>
       </c>
@@ -32429,7 +32429,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="503" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>502</v>
       </c>
@@ -32476,7 +32476,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="504" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>503</v>
       </c>
@@ -32526,7 +32526,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="505" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>504</v>
       </c>
@@ -32582,7 +32582,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="506" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>505</v>
       </c>
@@ -32641,7 +32641,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="507" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>506</v>
       </c>
@@ -32691,7 +32691,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="508" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>507</v>
       </c>
@@ -32738,7 +32738,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="509" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>508</v>
       </c>
@@ -32794,7 +32794,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="510" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>509</v>
       </c>
@@ -32850,7 +32850,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="511" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>510</v>
       </c>
@@ -32906,7 +32906,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="512" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>511</v>
       </c>
@@ -32962,7 +32962,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="513" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>512</v>
       </c>
@@ -33018,7 +33018,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="514" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>513</v>
       </c>
@@ -33071,7 +33071,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="515" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>514</v>
       </c>
@@ -33127,7 +33127,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="516" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>515</v>
       </c>
@@ -33180,7 +33180,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="517" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>516</v>
       </c>
@@ -33236,7 +33236,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="518" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>517</v>
       </c>
@@ -33292,7 +33292,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="519" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>518</v>
       </c>
@@ -33348,7 +33348,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="520" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>519</v>
       </c>
@@ -33404,7 +33404,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="521" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>520</v>
       </c>
@@ -33460,7 +33460,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="522" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>521</v>
       </c>
@@ -33516,7 +33516,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="523" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>522</v>
       </c>
@@ -33566,7 +33566,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="524" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>523</v>
       </c>
@@ -33622,7 +33622,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="525" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>524</v>
       </c>
@@ -33678,7 +33678,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="526" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>525</v>
       </c>
@@ -33725,7 +33725,7 @@
         <v>46056</v>
       </c>
     </row>
-    <row r="527" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>526</v>
       </c>
@@ -33772,7 +33772,7 @@
         <v>46056</v>
       </c>
     </row>
-    <row r="528" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>527</v>
       </c>
@@ -33819,7 +33819,7 @@
         <v>46056</v>
       </c>
     </row>
-    <row r="529" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>528</v>
       </c>
@@ -33866,7 +33866,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="530" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>529</v>
       </c>
@@ -33916,7 +33916,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="531" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>530</v>
       </c>
@@ -33975,7 +33975,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="532" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>531</v>
       </c>
@@ -34034,7 +34034,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="533" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>532</v>
       </c>
@@ -34084,7 +34084,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="534" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>533</v>
       </c>
@@ -34134,7 +34134,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="535" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>534</v>
       </c>
@@ -34184,7 +34184,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="536" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>535</v>
       </c>
@@ -34240,7 +34240,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="537" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>536</v>
       </c>
@@ -34293,7 +34293,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="538" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>537</v>
       </c>
@@ -34349,7 +34349,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="539" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>538</v>
       </c>
@@ -34408,7 +34408,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="540" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>539</v>
       </c>
@@ -34464,7 +34464,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="541" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>540</v>
       </c>
@@ -34520,7 +34520,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="542" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>541</v>
       </c>
@@ -34576,7 +34576,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="543" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>542</v>
       </c>
@@ -34635,7 +34635,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="544" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>543</v>
       </c>
@@ -34694,7 +34694,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="545" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>544</v>
       </c>
@@ -34750,7 +34750,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="546" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>545</v>
       </c>
@@ -34806,7 +34806,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="547" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>546</v>
       </c>
@@ -34862,7 +34862,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="548" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>547</v>
       </c>
@@ -34921,7 +34921,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="549" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>548</v>
       </c>
@@ -34980,7 +34980,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="550" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>549</v>
       </c>
@@ -35036,7 +35036,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="551" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>550</v>
       </c>
@@ -35095,7 +35095,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="552" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>551</v>
       </c>
@@ -35154,7 +35154,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="553" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>552</v>
       </c>
@@ -35213,7 +35213,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="554" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>553</v>
       </c>
@@ -35266,7 +35266,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="555" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>554</v>
       </c>
@@ -35325,7 +35325,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="556" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>555</v>
       </c>
@@ -35384,7 +35384,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="557" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>556</v>
       </c>
@@ -35440,7 +35440,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="558" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>557</v>
       </c>
@@ -35496,7 +35496,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="559" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>558</v>
       </c>
@@ -35552,7 +35552,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="560" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>559</v>
       </c>
@@ -35608,7 +35608,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="561" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>560</v>
       </c>
@@ -35664,7 +35664,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="562" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>561</v>
       </c>
@@ -35720,7 +35720,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="563" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>562</v>
       </c>
@@ -35776,7 +35776,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="564" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>563</v>
       </c>
@@ -35832,7 +35832,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="565" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>564</v>
       </c>
@@ -35888,7 +35888,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="566" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>565</v>
       </c>
@@ -35944,7 +35944,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="567" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>566</v>
       </c>
@@ -36000,7 +36000,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="568" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>567</v>
       </c>
@@ -36056,7 +36056,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="569" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>568</v>
       </c>
@@ -36103,7 +36103,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="570" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>569</v>
       </c>
@@ -36159,7 +36159,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="571" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>570</v>
       </c>
@@ -36215,7 +36215,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="572" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>571</v>
       </c>
@@ -36268,7 +36268,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="573" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>572</v>
       </c>
@@ -36324,7 +36324,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="574" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>573</v>
       </c>
@@ -36371,7 +36371,7 @@
         <v>46074</v>
       </c>
     </row>
-    <row r="575" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>574</v>
       </c>
@@ -36418,7 +36418,7 @@
         <v>46074</v>
       </c>
     </row>
-    <row r="576" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>575</v>
       </c>
@@ -36465,7 +36465,7 @@
         <v>46074</v>
       </c>
     </row>
-    <row r="577" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>576</v>
       </c>
@@ -36512,7 +36512,7 @@
         <v>46074</v>
       </c>
     </row>
-    <row r="578" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>577</v>
       </c>
@@ -36559,7 +36559,7 @@
         <v>46074</v>
       </c>
     </row>
-    <row r="579" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>578</v>
       </c>
@@ -36609,7 +36609,7 @@
         <v>46074</v>
       </c>
     </row>
-    <row r="580" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>579</v>
       </c>
@@ -36659,7 +36659,7 @@
         <v>46074</v>
       </c>
     </row>
-    <row r="581" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>580</v>
       </c>
@@ -36715,7 +36715,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="582" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>581</v>
       </c>
@@ -36774,7 +36774,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="583" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>582</v>
       </c>
@@ -36833,7 +36833,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="584" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>583</v>
       </c>
@@ -36892,7 +36892,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="585" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>584</v>
       </c>
@@ -36951,7 +36951,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="586" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>585</v>
       </c>
@@ -37010,7 +37010,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="587" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>586</v>
       </c>
@@ -37069,7 +37069,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="588" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>587</v>
       </c>
@@ -37128,7 +37128,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="589" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>588</v>
       </c>
@@ -37187,7 +37187,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="590" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>589</v>
       </c>
@@ -37243,7 +37243,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="591" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>590</v>
       </c>
@@ -37302,7 +37302,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="592" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>591</v>
       </c>
@@ -37358,7 +37358,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="593" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>592</v>
       </c>
@@ -37417,7 +37417,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="594" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>593</v>
       </c>
@@ -37476,7 +37476,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="595" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>594</v>
       </c>
@@ -37535,7 +37535,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="596" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>595</v>
       </c>
@@ -37594,7 +37594,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="597" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>596</v>
       </c>
@@ -37653,7 +37653,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="598" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>597</v>
       </c>
@@ -37709,7 +37709,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="599" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>598</v>
       </c>
@@ -37762,7 +37762,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="600" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>599</v>
       </c>
@@ -37818,7 +37818,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="601" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>600</v>
       </c>
@@ -37874,7 +37874,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="602" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>601</v>
       </c>
@@ -37930,7 +37930,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="603" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>602</v>
       </c>
@@ -37986,7 +37986,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="604" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>603</v>
       </c>
@@ -38042,7 +38042,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="605" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>604</v>
       </c>
@@ -38098,7 +38098,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="606" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>605</v>
       </c>
@@ -38154,7 +38154,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="607" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>606</v>
       </c>
@@ -38210,7 +38210,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="608" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A608">
         <v>607</v>
       </c>
@@ -38266,7 +38266,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="609" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>608</v>
       </c>
@@ -38322,7 +38322,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="610" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>609</v>
       </c>
@@ -38378,7 +38378,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="611" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>610</v>
       </c>
@@ -38434,7 +38434,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="612" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>611</v>
       </c>
@@ -38490,7 +38490,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="613" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>612</v>
       </c>
@@ -38549,7 +38549,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="614" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>613</v>
       </c>
@@ -38602,7 +38602,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="615" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>614</v>
       </c>
@@ -38658,7 +38658,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="616" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>615</v>
       </c>
@@ -38714,7 +38714,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="617" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>616</v>
       </c>
@@ -38770,7 +38770,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="618" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A618">
         <v>617</v>
       </c>
@@ -38826,7 +38826,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="619" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>618</v>
       </c>
@@ -38879,7 +38879,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="620" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>619</v>
       </c>
@@ -38935,7 +38935,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="621" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>620</v>
       </c>
@@ -38994,7 +38994,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="622" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>621</v>
       </c>
@@ -39053,7 +39053,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="623" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>622</v>
       </c>
@@ -39109,7 +39109,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="624" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>623</v>
       </c>
@@ -39168,7 +39168,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="625" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>624</v>
       </c>
@@ -39227,7 +39227,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="626" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>625</v>
       </c>
@@ -39274,7 +39274,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="627" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>626</v>
       </c>
@@ -39321,7 +39321,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="628" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>627</v>
       </c>
@@ -39368,7 +39368,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="629" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>628</v>
       </c>
@@ -39415,7 +39415,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="630" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>629</v>
       </c>
@@ -39474,7 +39474,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="631" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>630</v>
       </c>
@@ -39533,7 +39533,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="632" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A632">
         <v>631</v>
       </c>
@@ -39589,7 +39589,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="633" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A633">
         <v>632</v>
       </c>
@@ -39648,7 +39648,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="634" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>633</v>
       </c>
@@ -39704,7 +39704,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="635" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A635">
         <v>634</v>
       </c>
@@ -39760,7 +39760,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="636" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A636">
         <v>635</v>
       </c>
@@ -39819,7 +39819,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="637" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A637">
         <v>636</v>
       </c>
@@ -39878,7 +39878,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="638" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A638">
         <v>637</v>
       </c>
@@ -39937,7 +39937,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="639" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>638</v>
       </c>
@@ -39993,7 +39993,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="640" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A640">
         <v>639</v>
       </c>
@@ -40046,7 +40046,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="641" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A641">
         <v>640</v>
       </c>
@@ -40102,7 +40102,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="642" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A642">
         <v>641</v>
       </c>
@@ -40155,7 +40155,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="643" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A643">
         <v>642</v>
       </c>
@@ -40205,7 +40205,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="644" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A644">
         <v>643</v>
       </c>
@@ -40255,7 +40255,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="645" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>644</v>
       </c>
@@ -40305,7 +40305,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="646" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>645</v>
       </c>
@@ -40355,7 +40355,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="647" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>646</v>
       </c>
@@ -40402,7 +40402,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="648" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A648">
         <v>647</v>
       </c>
@@ -40452,7 +40452,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="649" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>648</v>
       </c>
@@ -40502,7 +40502,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="650" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A650">
         <v>649</v>
       </c>
@@ -40552,7 +40552,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="651" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A651">
         <v>650</v>
       </c>
@@ -40599,7 +40599,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="652" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A652">
         <v>651</v>
       </c>
@@ -40649,7 +40649,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="653" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A653">
         <v>652</v>
       </c>
@@ -40699,7 +40699,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="654" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A654">
         <v>653</v>
       </c>
@@ -40758,7 +40758,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="655" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A655">
         <v>654</v>
       </c>
@@ -40817,7 +40817,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="656" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A656">
         <v>655</v>
       </c>
@@ -40876,7 +40876,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="657" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A657">
         <v>656</v>
       </c>
@@ -40935,7 +40935,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="658" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A658">
         <v>657</v>
       </c>
@@ -40994,7 +40994,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="659" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A659">
         <v>658</v>
       </c>
@@ -41053,7 +41053,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="660" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A660">
         <v>659</v>
       </c>
@@ -41109,7 +41109,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="661" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A661">
         <v>660</v>
       </c>
@@ -41165,7 +41165,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="662" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A662">
         <v>661</v>
       </c>
@@ -41221,7 +41221,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="663" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A663">
         <v>662</v>
       </c>
@@ -41277,7 +41277,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="664" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A664">
         <v>663</v>
       </c>
@@ -41333,7 +41333,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="665" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A665">
         <v>664</v>
       </c>
@@ -41389,7 +41389,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="666" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A666">
         <v>665</v>
       </c>
@@ -41445,7 +41445,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="667" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A667">
         <v>666</v>
       </c>
@@ -41501,7 +41501,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="668" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A668">
         <v>667</v>
       </c>
@@ -41557,7 +41557,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="669" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A669">
         <v>668</v>
       </c>
@@ -41613,7 +41613,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="670" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A670">
         <v>669</v>
       </c>
@@ -41669,7 +41669,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="671" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A671">
         <v>670</v>
       </c>
@@ -41725,7 +41725,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="672" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A672">
         <v>671</v>
       </c>
@@ -41784,7 +41784,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="673" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A673">
         <v>672</v>
       </c>
@@ -41843,7 +41843,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="674" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A674">
         <v>673</v>
       </c>
@@ -41902,7 +41902,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="675" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A675">
         <v>674</v>
       </c>
@@ -41958,7 +41958,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="676" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A676">
         <v>675</v>
       </c>
@@ -42005,7 +42005,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="677" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A677">
         <v>676</v>
       </c>
@@ -42061,7 +42061,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="678" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A678">
         <v>677</v>
       </c>
@@ -42117,7 +42117,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="679" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A679">
         <v>678</v>
       </c>
@@ -42173,7 +42173,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="680" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A680">
         <v>679</v>
       </c>
@@ -42229,7 +42229,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="681" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A681">
         <v>680</v>
       </c>
@@ -42285,7 +42285,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="682" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A682">
         <v>681</v>
       </c>
@@ -42341,7 +42341,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="683" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A683">
         <v>682</v>
       </c>
@@ -42397,7 +42397,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="684" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A684">
         <v>683</v>
       </c>
@@ -42456,7 +42456,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="685" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A685">
         <v>684</v>
       </c>
@@ -42506,7 +42506,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="686" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A686">
         <v>685</v>
       </c>
@@ -42565,7 +42565,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="687" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A687">
         <v>686</v>
       </c>
@@ -42624,7 +42624,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="688" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A688">
         <v>687</v>
       </c>
@@ -42677,7 +42677,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="689" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A689">
         <v>688</v>
       </c>
@@ -42733,7 +42733,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="690" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A690">
         <v>689</v>
       </c>
@@ -42792,7 +42792,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="691" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A691">
         <v>690</v>
       </c>
@@ -42851,7 +42851,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="692" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A692">
         <v>691</v>
       </c>
@@ -42910,7 +42910,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="693" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A693">
         <v>692</v>
       </c>
@@ -42969,7 +42969,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="694" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A694">
         <v>693</v>
       </c>
@@ -43028,7 +43028,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="695" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A695">
         <v>694</v>
       </c>
@@ -43087,7 +43087,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="696" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A696">
         <v>695</v>
       </c>
@@ -43146,7 +43146,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="697" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A697">
         <v>696</v>
       </c>
@@ -43205,7 +43205,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="698" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A698">
         <v>697</v>
       </c>
@@ -43264,7 +43264,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="699" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A699">
         <v>698</v>
       </c>
@@ -43317,7 +43317,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="700" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A700">
         <v>699</v>
       </c>
@@ -43370,7 +43370,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="701" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A701">
         <v>700</v>
       </c>
@@ -43423,7 +43423,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="702" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A702">
         <v>701</v>
       </c>
@@ -43476,7 +43476,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="703" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A703">
         <v>702</v>
       </c>
@@ -43526,7 +43526,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="704" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A704">
         <v>703</v>
       </c>
@@ -43579,7 +43579,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="705" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A705">
         <v>704</v>
       </c>
@@ -43629,7 +43629,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="706" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A706">
         <v>705</v>
       </c>
@@ -43682,7 +43682,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="707" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A707">
         <v>706</v>
       </c>
@@ -43735,7 +43735,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="708" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A708">
         <v>707</v>
       </c>
@@ -43788,7 +43788,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="709" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A709">
         <v>708</v>
       </c>
@@ -43841,7 +43841,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="710" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A710">
         <v>709</v>
       </c>
@@ -43894,7 +43894,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="711" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A711">
         <v>710</v>
       </c>
@@ -43944,7 +43944,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="712" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A712">
         <v>711</v>
       </c>
@@ -43994,7 +43994,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="713" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A713">
         <v>712</v>
       </c>
@@ -44047,7 +44047,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="714" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A714">
         <v>713</v>
       </c>
@@ -44100,7 +44100,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="715" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A715">
         <v>714</v>
       </c>
@@ -44150,7 +44150,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="716" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A716">
         <v>715</v>
       </c>
@@ -44200,7 +44200,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="717" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A717">
         <v>716</v>
       </c>
@@ -44250,7 +44250,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="718" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A718">
         <v>717</v>
       </c>
@@ -44300,7 +44300,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="719" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A719">
         <v>718</v>
       </c>
@@ -44310,8 +44310,8 @@
       <c r="C719" s="1">
         <v>46106</v>
       </c>
-      <c r="D719" t="s">
-        <v>20</v>
+      <c r="D719" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="F719" t="s">
         <v>1057</v>
@@ -44349,8 +44349,11 @@
       <c r="R719" s="1">
         <v>46106</v>
       </c>
-    </row>
-    <row r="720" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S719" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="720" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A720">
         <v>719</v>
       </c>
@@ -44360,8 +44363,8 @@
       <c r="C720" s="1">
         <v>46106</v>
       </c>
-      <c r="D720" t="s">
-        <v>20</v>
+      <c r="D720" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="F720" t="s">
         <v>1719</v>
@@ -44396,8 +44399,11 @@
       <c r="R720" s="1">
         <v>46106</v>
       </c>
-    </row>
-    <row r="721" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S720" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="721" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A721">
         <v>720</v>
       </c>

--- a/data_pur.xlsx
+++ b/data_pur.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ali\belajar python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62376AC-1F40-4F28-B2C0-2176A1243298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA44EC53-6550-4F50-AF90-F31033E4DB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data_pur.xlsx
+++ b/data_pur.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ali\belajar python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4B76D4-489C-4B53-8A83-B9686F93487A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FD3500-24B0-44A9-BDC5-064401A9B981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
